--- a/data/trans_dic/P16A06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,4</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,37</t>
+          <t>0,23; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,89</t>
+          <t>0,25; 2,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,68</t>
+          <t>1,41; 7,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,17</t>
+          <t>0,18; 1,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,51</t>
+          <t>0,33; 1,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,35</t>
+          <t>0,12; 1,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,59</t>
+          <t>0,93; 4,82</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,56</t>
+          <t>0,26; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,26</t>
+          <t>0,29; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,05</t>
+          <t>0,08; 2,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,36</t>
+          <t>0,48; 2,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,31</t>
+          <t>0,27; 2,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,17</t>
+          <t>0,49; 2,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,1</t>
+          <t>0,49; 3,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,55</t>
+          <t>0,5; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,89</t>
+          <t>0,46; 1,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,31</t>
+          <t>0,4; 1,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,08</t>
+          <t>0,5; 2,14</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,49</t>
+          <t>0,69; 2,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,97</t>
+          <t>1,22; 4,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,05</t>
+          <t>0,28; 2,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,85</t>
+          <t>1,55; 4,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,61</t>
+          <t>1,37; 3,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,22</t>
+          <t>3,15; 6,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,53</t>
+          <t>1,37; 3,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,94</t>
+          <t>3,05; 5,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,68</t>
+          <t>1,22; 2,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,37</t>
+          <t>2,5; 4,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,33</t>
+          <t>0,98; 2,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,62</t>
+          <t>2,64; 4,88</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,58</t>
+          <t>0,85; 3,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,28</t>
+          <t>1,19; 4,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,55</t>
+          <t>1,73; 4,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,48</t>
+          <t>1,25; 5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,96</t>
+          <t>2,57; 6,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,78</t>
+          <t>3,8; 7,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,24</t>
+          <t>5,13; 9,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,59</t>
+          <t>6,42; 10,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,24</t>
+          <t>2,03; 4,19</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 5,33</t>
+          <t>2,83; 5,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,42</t>
+          <t>3,88; 6,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,28</t>
+          <t>3,32; 7,32</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,5</t>
+          <t>1,3; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,25</t>
+          <t>1,18; 4,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,98</t>
+          <t>2,15; 6,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,11</t>
+          <t>4,94; 9,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,03</t>
+          <t>4,4; 9,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,3; 10,2</t>
+          <t>5,2; 10,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 16,93</t>
+          <t>10,51; 16,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,19; 16,77</t>
+          <t>12,4; 16,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,33</t>
+          <t>3,13; 6,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,66</t>
+          <t>3,58; 6,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,62</t>
+          <t>6,76; 10,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,2</t>
+          <t>9,03; 12,18</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,88</t>
+          <t>3,08; 7,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,37</t>
+          <t>1,67; 6,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,33</t>
+          <t>4,9; 10,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,29</t>
+          <t>6,34; 11,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 12,13</t>
+          <t>6,64; 12,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 15,6</t>
+          <t>8,29; 14,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 21,83</t>
+          <t>13,96; 21,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,12</t>
+          <t>4,12; 16,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,24</t>
+          <t>5,53; 9,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,73; 10,2</t>
+          <t>5,86; 10,13</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,05; 15,25</t>
+          <t>10,28; 15,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,14</t>
+          <t>4,93; 13,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 11,88</t>
+          <t>4,91; 12,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,6</t>
+          <t>2,83; 8,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,21</t>
+          <t>5,75; 12,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 19,75</t>
+          <t>12,97; 19,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,94</t>
+          <t>7,31; 14,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,09; 23,4</t>
+          <t>15,0; 23,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,19; 20,09</t>
+          <t>11,99; 20,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,32; 30,64</t>
+          <t>24,18; 30,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 12,44</t>
+          <t>7,15; 12,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 16,83</t>
+          <t>11,0; 16,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,34; 16,0</t>
+          <t>9,97; 15,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,57; 25,23</t>
+          <t>20,58; 25,1</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,47</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,63</t>
+          <t>1,59; 2,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,31</t>
+          <t>2,1; 3,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,7</t>
+          <t>3,75; 5,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,86</t>
+          <t>3,5; 4,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,17</t>
+          <t>5,55; 7,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,4</t>
+          <t>6,62; 8,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,32; 10,99</t>
+          <t>7,96; 10,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 3,54</t>
+          <t>2,65; 3,51</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,68</t>
+          <t>3,79; 4,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 5,75</t>
+          <t>4,62; 5,72</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,39; 8,13</t>
+          <t>6,46; 8,16</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas</t>
+          <t>Población que ha consumido pastillas para dormir en las dos últimas semanas (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3314</t>
+          <t>0; 3795</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2044</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 21602</t>
+          <t>0; 23792</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1946; 11082</t>
+          <t>1080; 10537</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1980; 12336</t>
+          <t>1984; 12333</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1702; 11420</t>
+          <t>993; 11163</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5064; 27190</t>
+          <t>4423; 24140</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1872; 11218</t>
+          <t>1721; 10685</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2807; 13364</t>
+          <t>2926; 13229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>993; 11024</t>
+          <t>968; 12017</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6617; 32758</t>
+          <t>6650; 34378</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2011; 11458</t>
+          <t>1923; 11204</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2033; 15542</t>
+          <t>2008; 16159</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7020</t>
+          <t>0; 6306</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>339; 8703</t>
+          <t>340; 8957</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2981; 14737</t>
+          <t>2992; 14667</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1252; 14093</t>
+          <t>1633; 14784</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2782; 12240</t>
+          <t>2781; 13050</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2490; 15881</t>
+          <t>2529; 15669</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6428; 21133</t>
+          <t>6868; 21392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5839; 24522</t>
+          <t>5918; 23161</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4638; 15151</t>
+          <t>4579; 15387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4748; 19454</t>
+          <t>4667; 20043</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4403; 15880</t>
+          <t>4399; 16209</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8122; 26948</t>
+          <t>8269; 27982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1888; 13692</t>
+          <t>1852; 13767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8150; 26028</t>
+          <t>8336; 25874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9081; 24881</t>
+          <t>9444; 25743</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21953; 43888</t>
+          <t>22226; 43708</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8323; 23352</t>
+          <t>9039; 23384</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16029; 32219</t>
+          <t>16552; 32467</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15700; 35579</t>
+          <t>16128; 36203</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33095; 60481</t>
+          <t>34575; 62754</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13153; 30992</t>
+          <t>13077; 30395</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26953; 49833</t>
+          <t>28522; 52620</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4069; 18595</t>
+          <t>4414; 18526</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7378; 26322</t>
+          <t>7314; 24927</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10528; 29379</t>
+          <t>11182; 28944</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11047; 48635</t>
+          <t>11141; 48230</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13139; 30725</t>
+          <t>13277; 31233</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22400; 47716</t>
+          <t>23279; 48239</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32925; 59953</t>
+          <t>33271; 60174</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44880; 75497</t>
+          <t>45766; 76035</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20812; 43924</t>
+          <t>21050; 43335</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35575; 65455</t>
+          <t>34710; 65891</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49451; 83169</t>
+          <t>50230; 83233</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>56988; 116496</t>
+          <t>53165; 117211</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4620; 17411</t>
+          <t>5024; 17523</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5199; 18194</t>
+          <t>5048; 17493</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9953; 28593</t>
+          <t>10260; 28910</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27723; 51049</t>
+          <t>27681; 51201</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16555; 36483</t>
+          <t>17793; 37904</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23723; 45676</t>
+          <t>23290; 46400</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49959; 84116</t>
+          <t>52232; 82213</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>66408; 91343</t>
+          <t>67527; 90962</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25297; 50012</t>
+          <t>24762; 48351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31364; 58356</t>
+          <t>31406; 57594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66691; 103514</t>
+          <t>65939; 102934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>101339; 134838</t>
+          <t>99769; 134619</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8961; 23064</t>
+          <t>8998; 22701</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4909; 19619</t>
+          <t>5143; 19268</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16017; 34543</t>
+          <t>16383; 34683</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24638; 41562</t>
+          <t>23341; 41096</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20247; 41606</t>
+          <t>22785; 43389</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29826; 55082</t>
+          <t>29251; 52784</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52933; 82466</t>
+          <t>52724; 82553</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28450; 104172</t>
+          <t>25041; 102426</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35066; 58702</t>
+          <t>35168; 58824</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37858; 67432</t>
+          <t>38747; 66919</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71574; 108586</t>
+          <t>73176; 108239</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51819; 128352</t>
+          <t>48130; 130055</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>9403; 24941</t>
+          <t>10301; 25735</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7146; 21395</t>
+          <t>7052; 20722</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15027; 31379</t>
+          <t>14788; 31369</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36592; 55737</t>
+          <t>36609; 55997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23909; 46563</t>
+          <t>24404; 47443</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58346; 90508</t>
+          <t>58017; 90604</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48795; 80406</t>
+          <t>48000; 80657</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>103201; 130033</t>
+          <t>102633; 128544</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37817; 67638</t>
+          <t>38897; 66188</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69059; 106984</t>
+          <t>69921; 106573</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>67948; 105150</t>
+          <t>65525; 102962</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>145326; 178260</t>
+          <t>145423; 177366</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>50520; 80965</t>
+          <t>50187; 82874</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>52781; 90023</t>
+          <t>54220; 88623</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>73728; 112248</t>
+          <t>71362; 109099</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>131136; 196992</t>
+          <t>129731; 193911</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>116772; 164191</t>
+          <t>118361; 165057</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>192835; 254178</t>
+          <t>196652; 251511</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>234670; 297806</t>
+          <t>234505; 301382</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>304452; 401918</t>
+          <t>291033; 399005</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>180172; 235616</t>
+          <t>176275; 233535</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>258055; 326046</t>
+          <t>263880; 331559</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>318409; 399037</t>
+          <t>320372; 396633</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>455011; 578475</t>
+          <t>459592; 580537</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A06-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A06-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,25</t>
+          <t>0,38; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,87</t>
+          <t>0,47; 2,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,82</t>
+          <t>0,25; 3,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 7,71</t>
+          <t>1,31; 7,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,11</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,5</t>
+          <t>0,32; 1,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,47</t>
+          <t>0,21; 1,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,82</t>
+          <t>1,03; 4,45</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,52</t>
+          <t>0,26; 1,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,35</t>
+          <t>0,29; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,07</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,11</t>
+          <t>0,28; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,34</t>
+          <t>0,46; 2,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,43</t>
+          <t>0,27; 2,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,32</t>
+          <t>0,49; 2,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,06</t>
+          <t>0,57; 3,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,57</t>
+          <t>0,51; 1,58</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,79</t>
+          <t>0,43; 1,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,33</t>
+          <t>0,4; 1,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,14</t>
+          <t>0,64; 2,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,54</t>
+          <t>0,68; 2,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,12</t>
+          <t>1,32; 4,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,06</t>
+          <t>0,28; 2,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,82</t>
+          <t>1,32; 4,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,73</t>
+          <t>1,33; 3,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 6,19</t>
+          <t>3,07; 6,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,54</t>
+          <t>1,29; 3,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,99</t>
+          <t>2,89; 5,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,73</t>
+          <t>1,15; 2,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,53</t>
+          <t>2,42; 4,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,28</t>
+          <t>1,0; 2,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,88</t>
+          <t>2,41; 4,47</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,57</t>
+          <t>0,83; 3,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,06</t>
+          <t>1,36; 4,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,48</t>
+          <t>1,74; 4,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,43</t>
+          <t>3,34; 6,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,06</t>
+          <t>2,47; 6,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,87</t>
+          <t>3,66; 7,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 9,27</t>
+          <t>5,16; 8,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,67</t>
+          <t>6,13; 9,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,19</t>
+          <t>2,05; 4,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,37</t>
+          <t>2,87; 5,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 6,43</t>
+          <t>3,74; 6,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 7,32</t>
+          <t>5,2; 7,49</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,53</t>
+          <t>1,32; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,08</t>
+          <t>1,03; 3,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,05</t>
+          <t>2,11; 6,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 9,14</t>
+          <t>4,83; 8,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,38</t>
+          <t>4,37; 9,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,36</t>
+          <t>5,34; 10,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,55</t>
+          <t>10,3; 16,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,7</t>
+          <t>12,33; 16,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,11</t>
+          <t>3,13; 6,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,57</t>
+          <t>3,62; 6,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,56</t>
+          <t>6,94; 10,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,18</t>
+          <t>8,95; 11,87</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,76</t>
+          <t>3,06; 7,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,26</t>
+          <t>1,59; 6,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,37</t>
+          <t>4,92; 10,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,16</t>
+          <t>6,11; 10,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 12,65</t>
+          <t>6,3; 12,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,95</t>
+          <t>8,37; 15,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,96; 21,85</t>
+          <t>13,6; 21,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,12; 16,84</t>
+          <t>13,95; 19,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,26</t>
+          <t>5,41; 9,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,13</t>
+          <t>5,69; 10,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,2</t>
+          <t>10,43; 15,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,93; 13,32</t>
+          <t>11,16; 14,5</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 12,26</t>
+          <t>4,72; 12,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,33</t>
+          <t>2,71; 8,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,21</t>
+          <t>5,76; 12,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,84</t>
+          <t>12,82; 19,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,21</t>
+          <t>7,14; 14,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0; 23,43</t>
+          <t>15,15; 23,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,99; 20,16</t>
+          <t>11,57; 20,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,18; 30,29</t>
+          <t>24,21; 30,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 12,17</t>
+          <t>7,2; 12,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 16,77</t>
+          <t>10,79; 16,15</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,97; 15,67</t>
+          <t>10,47; 16,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,58; 25,1</t>
+          <t>20,47; 25,14</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,53</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,52; 2,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,21</t>
+          <t>2,14; 3,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 5,61</t>
+          <t>4,49; 5,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 4,88</t>
+          <t>3,51; 4,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,09</t>
+          <t>5,54; 7,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 8,5</t>
+          <t>6,7; 8,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,96; 10,91</t>
+          <t>9,58; 11,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,51</t>
+          <t>2,71; 3,52</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,76</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 5,72</t>
+          <t>4,62; 5,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,16</t>
+          <t>7,29; 8,41</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>17788</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3795</t>
+          <t>0; 4560</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2083,47 +2083,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 23792</t>
+          <t>0; 18939</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1080; 10537</t>
+          <t>1792; 11091</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1984; 12333</t>
+          <t>1996; 12460</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>993; 11163</t>
+          <t>1003; 12299</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4423; 24140</t>
+          <t>4748; 27253</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1721; 10685</t>
+          <t>1798; 10583</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2926; 13229</t>
+          <t>2852; 14279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>968; 12017</t>
+          <t>1688; 12360</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6650; 34378</t>
+          <t>7897; 34240</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>12834</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1923; 11204</t>
+          <t>1891; 11518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2008; 16159</t>
+          <t>1966; 15609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6306</t>
+          <t>0; 6956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>340; 8957</t>
+          <t>1339; 12301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2992; 14667</t>
+          <t>2872; 14719</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1633; 14784</t>
+          <t>1627; 14009</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2781; 13050</t>
+          <t>2763; 13116</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2529; 15669</t>
+          <t>2859; 15040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6868; 21392</t>
+          <t>6983; 21570</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5918; 23161</t>
+          <t>5597; 23658</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4579; 15387</t>
+          <t>4560; 16139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4667; 20043</t>
+          <t>6249; 23715</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15205</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>25014</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>40655</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4399; 16209</t>
+          <t>4305; 17166</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8269; 27982</t>
+          <t>8994; 28475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1852; 13767</t>
+          <t>1855; 13507</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8336; 25874</t>
+          <t>8213; 26390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9444; 25743</t>
+          <t>9205; 24110</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22226; 43708</t>
+          <t>21676; 44150</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9039; 23384</t>
+          <t>8544; 23275</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16552; 32467</t>
+          <t>17970; 34301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16128; 36203</t>
+          <t>15319; 35114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34575; 62754</t>
+          <t>33464; 61700</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13077; 30395</t>
+          <t>13246; 31104</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28522; 52620</t>
+          <t>29920; 55575</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>56112</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>89297</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4414; 18526</t>
+          <t>4302; 19043</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7314; 24927</t>
+          <t>8361; 25312</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11182; 28944</t>
+          <t>11255; 29398</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11141; 48230</t>
+          <t>23421; 48429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13277; 31233</t>
+          <t>12735; 31477</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23279; 48239</t>
+          <t>22407; 46301</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33271; 60174</t>
+          <t>33524; 58051</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45766; 76035</t>
+          <t>45157; 68448</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21050; 43335</t>
+          <t>21195; 43416</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34710; 65891</t>
+          <t>35211; 64912</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50230; 83233</t>
+          <t>48373; 81221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53165; 117211</t>
+          <t>74648; 107576</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37866</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79077</t>
+          <t>87169</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>116943</t>
+          <t>126223</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5024; 17523</t>
+          <t>5114; 18113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5048; 17493</t>
+          <t>4428; 16715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10260; 28910</t>
+          <t>10100; 28746</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27681; 51201</t>
+          <t>29400; 51072</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17793; 37904</t>
+          <t>17656; 37493</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23290; 46400</t>
+          <t>23899; 46277</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52232; 82213</t>
+          <t>51195; 82631</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>67527; 90962</t>
+          <t>74786; 102463</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24762; 48351</t>
+          <t>24737; 48163</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31406; 57594</t>
+          <t>31738; 58436</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>65939; 102934</t>
+          <t>67614; 103983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99769; 134619</t>
+          <t>108775; 144204</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32160</t>
+          <t>34113</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>64861</t>
+          <t>72967</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>107080</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8998; 22701</t>
+          <t>8954; 22729</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5143; 19268</t>
+          <t>4879; 18914</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16383; 34683</t>
+          <t>16455; 35260</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23341; 41096</t>
+          <t>24881; 43918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22785; 43389</t>
+          <t>21597; 42370</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29251; 52784</t>
+          <t>29557; 53694</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52724; 82553</t>
+          <t>51386; 82021</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25041; 102426</t>
+          <t>61285; 84235</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35168; 58824</t>
+          <t>34406; 59449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38747; 66919</t>
+          <t>37604; 66170</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>73176; 108239</t>
+          <t>74303; 110299</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48130; 130055</t>
+          <t>94443; 122731</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45151</t>
+          <t>49317</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>115874</t>
+          <t>125807</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>161025</t>
+          <t>175124</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10301; 25735</t>
+          <t>9913; 26786</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7052; 20722</t>
+          <t>6750; 20815</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14788; 31369</t>
+          <t>14792; 31899</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36609; 55997</t>
+          <t>39716; 60783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>24404; 47443</t>
+          <t>23827; 47865</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>58017; 90604</t>
+          <t>58602; 89048</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48000; 80657</t>
+          <t>46303; 81133</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>102633; 128544</t>
+          <t>112130; 140096</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38897; 66188</t>
+          <t>39156; 67119</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>69921; 106573</t>
+          <t>68601; 102672</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65525; 102962</t>
+          <t>68818; 105243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>145423; 177366</t>
+          <t>158202; 194251</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>167783</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>359919</t>
+          <t>387229</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>527702</t>
+          <t>569001</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>50187; 82874</t>
+          <t>51342; 83533</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>54220; 88623</t>
+          <t>51830; 89358</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>71362; 109099</t>
+          <t>72586; 113046</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129731; 193911</t>
+          <t>158617; 210388</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>118361; 165057</t>
+          <t>118772; 165490</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>196652; 251511</t>
+          <t>196237; 252201</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>234505; 301382</t>
+          <t>237364; 302058</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>291033; 399005</t>
+          <t>357335; 418483</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>176275; 233535</t>
+          <t>180315; 234048</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>263880; 331559</t>
+          <t>260782; 331267</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>320372; 396633</t>
+          <t>320580; 395757</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>459592; 580537</t>
+          <t>529545; 610851</t>
         </is>
       </c>
     </row>
